--- a/Draft_LAPAS.xlsx
+++ b/Draft_LAPAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\vcr automasi - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81470FA6-5820-4764-B375-B3F1823D05CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E94D5E1-2B32-472C-93E7-FC54EF088DED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{EBCE3EDF-1BC9-40ED-97DD-F136F3E95562}"/>
   </bookViews>
@@ -703,8 +703,8 @@
     </row>
     <row r="15" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
-        <f>"NEGARA KELAS I PONDOK BAMBU"&amp;" untuk barang terlampir:"</f>
-        <v>NEGARA KELAS I PONDOK BAMBU untuk barang terlampir:</v>
+        <f>C10&amp;" untuk barang terlampir:"</f>
+        <v>RUMAH TAHANAN NEGARA KELAS I PONDOK BAMBU untuk barang terlampir:</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">

--- a/Draft_LAPAS.xlsx
+++ b/Draft_LAPAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\vcr automasi - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E94D5E1-2B32-472C-93E7-FC54EF088DED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA00D20-2C05-4D39-8ADF-8EAE02F82D6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{EBCE3EDF-1BC9-40ED-97DD-F136F3E95562}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Nomor</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>: Penawaran Harga Barang</t>
-  </si>
-  <si>
-    <t>RUMAH TAHANAN NEGARA KELAS I PONDOK BAMBU</t>
   </si>
   <si>
     <t>Di tempat</t>
@@ -678,13 +675,11 @@
         <f>"Kepada  Yth. PIMPINAN "</f>
         <v xml:space="preserve">Kepada  Yth. PIMPINAN </v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>5</v>
-      </c>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -692,24 +687,24 @@
     </row>
     <row r="13" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
-        <f>"Melalui surat ini kami bermaksud mengajukan penawaran kepada Bapak/Ibu Pimpinan"</f>
-        <v>Melalui surat ini kami bermaksud mengajukan penawaran kepada Bapak/Ibu Pimpinan</v>
+        <f>"Melalui surat ini kami bermaksud mengajukan penawaran kepada Bapak/Ibu Pimpinan "&amp;IFERROR(LEFT(C10, FIND(" ", C10, FIND(" ", C10) + 1) - 1), C10)</f>
+        <v xml:space="preserve">Melalui surat ini kami bermaksud mengajukan penawaran kepada Bapak/Ibu Pimpinan </v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
-        <f>C10&amp;" untuk barang terlampir:"</f>
-        <v>RUMAH TAHANAN NEGARA KELAS I PONDOK BAMBU untuk barang terlampir:</v>
+        <f>IFERROR(MID(C10, FIND(" ", C10, FIND(" ", C10) + 1) + 1, LEN(C10)), "")&amp;"untuk barang terlampir:"</f>
+        <v>untuk barang terlampir:</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -720,18 +715,18 @@
     </row>
     <row r="19" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" s="7"/>
     </row>
@@ -745,12 +740,12 @@
     </row>
     <row r="24" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I29" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -761,12 +756,12 @@
     </row>
     <row r="34" spans="9:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I34" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="9:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I35" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
